--- a/tabela_shopee.xlsx
+++ b/tabela_shopee.xlsx
@@ -1,15 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rodrigo\Desktop\Shopee_Bot_Orcamentos\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E51BF7D8-97DB-439A-9C23-36C52C26EEA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -22,8 +33,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -86,11 +97,19 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -132,7 +151,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -164,9 +183,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -198,6 +235,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -373,11 +428,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P32"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -412,7 +467,7 @@
         <v>1</v>
       </c>
       <c r="L1" s="1">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="M1" s="1">
         <v>1.2</v>
@@ -427,1554 +482,1554 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B2">
-        <v>160</v>
+        <v>0.1</v>
       </c>
       <c r="C2">
-        <v>160</v>
+        <v>0.2</v>
       </c>
       <c r="D2">
-        <v>160</v>
+        <v>0.3</v>
       </c>
       <c r="E2">
-        <v>160</v>
+        <v>0.4</v>
       </c>
       <c r="F2">
-        <v>160</v>
+        <v>0.5</v>
       </c>
       <c r="G2">
-        <v>160</v>
+        <v>0.6</v>
       </c>
       <c r="H2">
-        <v>160</v>
+        <v>0.7</v>
       </c>
       <c r="I2">
-        <v>160</v>
+        <v>0.8</v>
       </c>
       <c r="J2">
-        <v>160</v>
+        <v>0.9</v>
       </c>
       <c r="K2">
-        <v>160</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>165</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="M2">
-        <v>165</v>
+        <v>1.2</v>
       </c>
       <c r="N2">
-        <v>195</v>
+        <v>1.3</v>
       </c>
       <c r="O2">
-        <v>195</v>
+        <v>1.4</v>
       </c>
       <c r="P2">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>2.9</v>
+        <v>0.1</v>
       </c>
       <c r="B3">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="C3">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="D3">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="E3">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="F3">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="G3">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="H3">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="I3">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="J3">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="K3">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="L3">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="M3">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="N3">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="O3">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="P3">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>2.8</v>
+        <v>0.2</v>
       </c>
       <c r="B4">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="C4">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="D4">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="E4">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="F4">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="G4">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="H4">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="I4">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="J4">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="K4">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="L4">
-        <v>160</v>
+        <v>70</v>
       </c>
       <c r="M4">
-        <v>160</v>
+        <v>70</v>
       </c>
       <c r="N4">
-        <v>185</v>
+        <v>70</v>
       </c>
       <c r="O4">
-        <v>185</v>
+        <v>70</v>
       </c>
       <c r="P4">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>2.7</v>
+        <v>0.3</v>
       </c>
       <c r="B5">
-        <v>140</v>
+        <v>65</v>
       </c>
       <c r="C5">
-        <v>140</v>
+        <v>65</v>
       </c>
       <c r="D5">
-        <v>140</v>
+        <v>65</v>
       </c>
       <c r="E5">
-        <v>140</v>
+        <v>65</v>
       </c>
       <c r="F5">
-        <v>140</v>
+        <v>65</v>
       </c>
       <c r="G5">
-        <v>140</v>
+        <v>65</v>
       </c>
       <c r="H5">
-        <v>140</v>
+        <v>65</v>
       </c>
       <c r="I5">
-        <v>140</v>
+        <v>65</v>
       </c>
       <c r="J5">
-        <v>140</v>
+        <v>65</v>
       </c>
       <c r="K5">
-        <v>140</v>
+        <v>65</v>
       </c>
       <c r="L5">
-        <v>160</v>
+        <v>70</v>
       </c>
       <c r="M5">
-        <v>160</v>
+        <v>70</v>
       </c>
       <c r="N5">
-        <v>180</v>
+        <v>70</v>
       </c>
       <c r="O5">
-        <v>180</v>
+        <v>70</v>
       </c>
       <c r="P5">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="B6">
-        <v>135</v>
+        <v>65</v>
       </c>
       <c r="C6">
-        <v>135</v>
+        <v>65</v>
       </c>
       <c r="D6">
-        <v>135</v>
+        <v>65</v>
       </c>
       <c r="E6">
-        <v>135</v>
+        <v>65</v>
       </c>
       <c r="F6">
-        <v>135</v>
+        <v>65</v>
       </c>
       <c r="G6">
-        <v>135</v>
+        <v>65</v>
       </c>
       <c r="H6">
-        <v>135</v>
+        <v>65</v>
       </c>
       <c r="I6">
-        <v>135</v>
+        <v>65</v>
       </c>
       <c r="J6">
-        <v>135</v>
+        <v>65</v>
       </c>
       <c r="K6">
-        <v>135</v>
+        <v>65</v>
       </c>
       <c r="L6">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="M6">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="N6">
-        <v>175</v>
+        <v>70</v>
       </c>
       <c r="O6">
-        <v>175</v>
+        <v>70</v>
       </c>
       <c r="P6">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="B7">
-        <v>135</v>
+        <v>65</v>
       </c>
       <c r="C7">
-        <v>135</v>
+        <v>65</v>
       </c>
       <c r="D7">
-        <v>135</v>
+        <v>65</v>
       </c>
       <c r="E7">
-        <v>135</v>
+        <v>65</v>
       </c>
       <c r="F7">
-        <v>135</v>
+        <v>65</v>
       </c>
       <c r="G7">
-        <v>135</v>
+        <v>65</v>
       </c>
       <c r="H7">
-        <v>135</v>
+        <v>65</v>
       </c>
       <c r="I7">
-        <v>135</v>
+        <v>65</v>
       </c>
       <c r="J7">
-        <v>135</v>
+        <v>65</v>
       </c>
       <c r="K7">
-        <v>135</v>
+        <v>65</v>
       </c>
       <c r="L7">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="M7">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="N7">
-        <v>170</v>
+        <v>70</v>
       </c>
       <c r="O7">
-        <v>170</v>
+        <v>70</v>
       </c>
       <c r="P7">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="B8">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="C8">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="D8">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="E8">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="F8">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="G8">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="H8">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="I8">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="J8">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="K8">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="L8">
-        <v>145</v>
+        <v>70</v>
       </c>
       <c r="M8">
-        <v>145</v>
+        <v>70</v>
       </c>
       <c r="N8">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="O8">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="P8">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="B9">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="C9">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="D9">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="E9">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="F9">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="G9">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="H9">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="I9">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="J9">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="K9">
-        <v>125</v>
+        <v>70</v>
       </c>
       <c r="L9">
-        <v>140</v>
+        <v>70</v>
       </c>
       <c r="M9">
-        <v>140</v>
+        <v>70</v>
       </c>
       <c r="N9">
-        <v>160</v>
+        <v>70</v>
       </c>
       <c r="O9">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="P9">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="B10">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="C10">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="D10">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="E10">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="F10">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="G10">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="H10">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="I10">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="J10">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="K10">
-        <v>125</v>
+        <v>70</v>
       </c>
       <c r="L10">
-        <v>135</v>
+        <v>70</v>
       </c>
       <c r="M10">
-        <v>135</v>
+        <v>70</v>
       </c>
       <c r="N10">
-        <v>155</v>
+        <v>75</v>
       </c>
       <c r="O10">
-        <v>155</v>
+        <v>75</v>
       </c>
       <c r="P10">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="B11">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="C11">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="D11">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="E11">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="F11">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="G11">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="H11">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="I11">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="J11">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="K11">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="L11">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="M11">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="N11">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="O11">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="P11">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B12">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="C12">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="D12">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="E12">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="F12">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="G12">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="H12">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="I12">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="J12">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="K12">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="L12">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="M12">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="N12">
-        <v>145</v>
+        <v>75</v>
       </c>
       <c r="O12">
-        <v>145</v>
+        <v>78</v>
       </c>
       <c r="P12">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
-        <v>1.9</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="B13">
-        <v>115</v>
+        <v>70</v>
       </c>
       <c r="C13">
-        <v>115</v>
+        <v>70</v>
       </c>
       <c r="D13">
-        <v>115</v>
+        <v>70</v>
       </c>
       <c r="E13">
-        <v>115</v>
+        <v>70</v>
       </c>
       <c r="F13">
-        <v>115</v>
+        <v>70</v>
       </c>
       <c r="G13">
-        <v>115</v>
+        <v>70</v>
       </c>
       <c r="H13">
-        <v>115</v>
+        <v>70</v>
       </c>
       <c r="I13">
-        <v>115</v>
+        <v>70</v>
       </c>
       <c r="J13">
-        <v>115</v>
+        <v>70</v>
       </c>
       <c r="K13">
-        <v>115</v>
+        <v>70</v>
       </c>
       <c r="L13">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="M13">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="N13">
-        <v>140</v>
+        <v>75</v>
       </c>
       <c r="O13">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="P13">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="B14">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="C14">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="D14">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="E14">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="F14">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="G14">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="H14">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="I14">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="J14">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="K14">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="L14">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="M14">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="N14">
-        <v>135</v>
+        <v>75</v>
       </c>
       <c r="O14">
-        <v>135</v>
+        <v>78</v>
       </c>
       <c r="P14">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="B15">
-        <v>105</v>
+        <v>70</v>
       </c>
       <c r="C15">
-        <v>105</v>
+        <v>70</v>
       </c>
       <c r="D15">
-        <v>105</v>
+        <v>70</v>
       </c>
       <c r="E15">
-        <v>105</v>
+        <v>70</v>
       </c>
       <c r="F15">
-        <v>105</v>
+        <v>70</v>
       </c>
       <c r="G15">
-        <v>105</v>
+        <v>70</v>
       </c>
       <c r="H15">
-        <v>105</v>
+        <v>70</v>
       </c>
       <c r="I15">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="J15">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="K15">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="L15">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="M15">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="N15">
-        <v>135</v>
+        <v>78</v>
       </c>
       <c r="O15">
-        <v>135</v>
+        <v>78</v>
       </c>
       <c r="P15">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="B16">
-        <v>105</v>
+        <v>70</v>
       </c>
       <c r="C16">
-        <v>105</v>
+        <v>70</v>
       </c>
       <c r="D16">
-        <v>105</v>
+        <v>70</v>
       </c>
       <c r="E16">
-        <v>105</v>
+        <v>70</v>
       </c>
       <c r="F16">
-        <v>105</v>
+        <v>70</v>
       </c>
       <c r="G16">
-        <v>105</v>
+        <v>70</v>
       </c>
       <c r="H16">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="I16">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="J16">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="K16">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L16">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="M16">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="N16">
-        <v>130</v>
+        <v>78</v>
       </c>
       <c r="O16">
-        <v>130</v>
+        <v>78</v>
       </c>
       <c r="P16">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>1.5</v>
       </c>
       <c r="B17">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="C17">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="D17">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="E17">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F17">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="G17">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="H17">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="I17">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="J17">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="K17">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="L17">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="M17">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="N17">
-        <v>125</v>
+        <v>78</v>
       </c>
       <c r="O17">
-        <v>125</v>
+        <v>78</v>
       </c>
       <c r="P17">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="B18">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="C18">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="D18">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="E18">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="F18">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="G18">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="H18">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="I18">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="J18">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="K18">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="L18">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="M18">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="N18">
-        <v>120</v>
+        <v>78</v>
       </c>
       <c r="O18">
-        <v>120</v>
+        <v>78</v>
       </c>
       <c r="P18">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="B19">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="C19">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="D19">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="E19">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="F19">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="G19">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="H19">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="I19">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="J19">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="K19">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="L19">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="M19">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="N19">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="O19">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="P19">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="B20">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="C20">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D20">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="E20">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="F20">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G20">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="H20">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I20">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J20">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K20">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="L20">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="M20">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="N20">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="O20">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="P20">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="B21">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="C21">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="D21">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="E21">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="F21">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="G21">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="H21">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="I21">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="J21">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="K21">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="L21">
-        <v>95</v>
+        <v>150</v>
       </c>
       <c r="M21">
-        <v>95</v>
+        <v>150</v>
       </c>
       <c r="N21">
-        <v>105</v>
+        <v>150</v>
       </c>
       <c r="O21">
-        <v>105</v>
+        <v>150</v>
       </c>
       <c r="P21">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B22">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="C22">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="D22">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="E22">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="F22">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="G22">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="H22">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="I22">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="J22">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="K22">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="L22">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="M22">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="N22">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="O22">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="P22">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="B23">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="C23">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="D23">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="E23">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="F23">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="G23">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="H23">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="I23">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="J23">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="K23">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="L23">
-        <v>85</v>
+        <v>150</v>
       </c>
       <c r="M23">
-        <v>85</v>
+        <v>150</v>
       </c>
       <c r="N23">
-        <v>95</v>
+        <v>150</v>
       </c>
       <c r="O23">
-        <v>95</v>
+        <v>150</v>
       </c>
       <c r="P23">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
-        <v>0.8</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="B24">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="C24">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="D24">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="E24">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="F24">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="G24">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="H24">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="I24">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="J24">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="K24">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="L24">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="M24">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="N24">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="O24">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="P24">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
-        <v>0.7</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="B25">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="C25">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="D25">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="E25">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="F25">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="G25">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="H25">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="I25">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="J25">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="K25">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="L25">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="M25">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="N25">
-        <v>85</v>
+        <v>180</v>
       </c>
       <c r="O25">
-        <v>85</v>
+        <v>180</v>
       </c>
       <c r="P25">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="B26">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="C26">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="D26">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="E26">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="F26">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="G26">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="H26">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="I26">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="J26">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="K26">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="L26">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="M26">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="N26">
-        <v>80</v>
+        <v>180</v>
       </c>
       <c r="O26">
-        <v>80</v>
+        <v>180</v>
       </c>
       <c r="P26">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="B27">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="C27">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="D27">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="E27">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="F27">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="G27">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="H27">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="I27">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="J27">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="K27">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="L27">
-        <v>70</v>
+        <v>180</v>
       </c>
       <c r="M27">
-        <v>70</v>
+        <v>180</v>
       </c>
       <c r="N27">
-        <v>75</v>
+        <v>180</v>
       </c>
       <c r="O27">
-        <v>75</v>
+        <v>180</v>
       </c>
       <c r="P27">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
       <c r="B28">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="C28">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="D28">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="E28">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="F28">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="G28">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="H28">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="I28">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="J28">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="K28">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="L28">
-        <v>65</v>
+        <v>180</v>
       </c>
       <c r="M28">
-        <v>65</v>
+        <v>180</v>
       </c>
       <c r="N28">
-        <v>70</v>
+        <v>180</v>
       </c>
       <c r="O28">
-        <v>70</v>
+        <v>180</v>
       </c>
       <c r="P28">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
-        <v>0.3</v>
+        <v>2.7</v>
       </c>
       <c r="B29">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="C29">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="D29">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="E29">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="F29">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="G29">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="H29">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="I29">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="J29">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="K29">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="L29">
-        <v>65</v>
+        <v>180</v>
       </c>
       <c r="M29">
-        <v>65</v>
+        <v>180</v>
       </c>
       <c r="N29">
-        <v>65</v>
+        <v>180</v>
       </c>
       <c r="O29">
-        <v>65</v>
+        <v>180</v>
       </c>
       <c r="P29">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
-        <v>0.2</v>
+        <v>2.8</v>
       </c>
       <c r="B30">
-        <v>55</v>
+        <v>180</v>
       </c>
       <c r="C30">
-        <v>55</v>
+        <v>180</v>
       </c>
       <c r="D30">
-        <v>55</v>
+        <v>180</v>
       </c>
       <c r="E30">
-        <v>55</v>
+        <v>180</v>
       </c>
       <c r="F30">
-        <v>55</v>
+        <v>180</v>
       </c>
       <c r="G30">
-        <v>55</v>
+        <v>180</v>
       </c>
       <c r="H30">
-        <v>55</v>
+        <v>180</v>
       </c>
       <c r="I30">
-        <v>55</v>
+        <v>180</v>
       </c>
       <c r="J30">
-        <v>55</v>
+        <v>180</v>
       </c>
       <c r="K30">
-        <v>55</v>
+        <v>180</v>
       </c>
       <c r="L30">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="M30">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="N30">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="O30">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="P30">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
-        <v>0.1</v>
+        <v>2.9</v>
       </c>
       <c r="B31">
-        <v>55</v>
+        <v>180</v>
       </c>
       <c r="C31">
-        <v>55</v>
+        <v>180</v>
       </c>
       <c r="D31">
-        <v>55</v>
+        <v>180</v>
       </c>
       <c r="E31">
-        <v>55</v>
+        <v>180</v>
       </c>
       <c r="F31">
-        <v>55</v>
+        <v>180</v>
       </c>
       <c r="G31">
-        <v>55</v>
+        <v>180</v>
       </c>
       <c r="H31">
-        <v>55</v>
+        <v>180</v>
       </c>
       <c r="I31">
-        <v>55</v>
+        <v>180</v>
       </c>
       <c r="J31">
-        <v>55</v>
+        <v>180</v>
       </c>
       <c r="K31">
-        <v>55</v>
+        <v>180</v>
       </c>
       <c r="L31">
-        <v>55</v>
+        <v>200</v>
       </c>
       <c r="M31">
-        <v>55</v>
+        <v>200</v>
       </c>
       <c r="N31">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="O31">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="P31">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B32">
-        <v>0.1</v>
+        <v>200</v>
       </c>
       <c r="C32">
-        <v>0.2</v>
+        <v>200</v>
       </c>
       <c r="D32">
-        <v>0.3</v>
+        <v>200</v>
       </c>
       <c r="E32">
-        <v>0.4</v>
+        <v>200</v>
       </c>
       <c r="F32">
-        <v>0.5</v>
+        <v>200</v>
       </c>
       <c r="G32">
-        <v>0.6</v>
+        <v>200</v>
       </c>
       <c r="H32">
-        <v>0.7</v>
+        <v>200</v>
       </c>
       <c r="I32">
-        <v>0.8</v>
+        <v>200</v>
       </c>
       <c r="J32">
-        <v>0.9</v>
+        <v>200</v>
       </c>
       <c r="K32">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="L32">
-        <v>1.1</v>
+        <v>200</v>
       </c>
       <c r="M32">
-        <v>1.2</v>
+        <v>200</v>
       </c>
       <c r="N32">
-        <v>1.3</v>
+        <v>200</v>
       </c>
       <c r="O32">
-        <v>1.4</v>
+        <v>200</v>
       </c>
       <c r="P32">
-        <v>1.5</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>

--- a/tabela_shopee.xlsx
+++ b/tabela_shopee.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rodrigo\Desktop\Shopee_Bot_Orcamentos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E51BF7D8-97DB-439A-9C23-36C52C26EEA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B9B7605-E641-4B3F-B8EA-3A9479F2A706}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
